--- a/assets/frequency_report_template.xlsx
+++ b/assets/frequency_report_template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10916"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/natashasoldin/Documents/Work/Sunrise Frequency Reporting/Sunrise-Frequency-Reporting/assets/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://itcentricsx-my.sharepoint.com/personal/elijah_sunriselogistics_net/Documents/Desktop/Sunrise_Reporting/assets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6104D93-DB58-0C43-AA84-E70EE2984091}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="49" documentId="13_ncr:1_{C6104D93-DB58-0C43-AA84-E70EE2984091}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BCF1F762-DF38-4F48-8004-B302001812E2}"/>
   <bookViews>
-    <workbookView xWindow="37180" yWindow="5400" windowWidth="28040" windowHeight="17440" xr2:uid="{38A25583-7701-1647-97E3-DC304504240B}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{38A25583-7701-1647-97E3-DC304504240B}"/>
   </bookViews>
   <sheets>
     <sheet name="Current deliveries" sheetId="3" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="9">
   <si>
     <t>FREQUENCY REPORT</t>
   </si>
@@ -46,12 +46,30 @@
   <si>
     <t>date_time</t>
   </si>
+  <si>
+    <t>Legend</t>
+  </si>
+  <si>
+    <t>Delivered</t>
+  </si>
+  <si>
+    <t>Query By Sunrise</t>
+  </si>
+  <si>
+    <t>On Delivery</t>
+  </si>
+  <si>
+    <t>Future Delivery</t>
+  </si>
+  <si>
+    <t>For Client</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -81,16 +99,72 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="26"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="26"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B0F0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE49EDD"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -98,16 +172,28 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -116,6 +202,33 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -145,9 +258,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>584200</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>101600</xdr:rowOff>
+      <xdr:colOff>588010</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>21590</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -232,10 +345,14 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -273,7 +390,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -379,7 +496,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -521,7 +638,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -529,87 +646,112 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC63E38F-1972-EF43-B9EA-2E28A018FDEC}">
-  <dimension ref="A1:H8"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:J8"/>
+  <sheetFormatPr defaultColWidth="11.19921875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A1" s="1"/>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-    </row>
-    <row r="3" spans="1:8" ht="29" x14ac:dyDescent="0.35">
-      <c r="A3" s="1"/>
-      <c r="B3" s="1"/>
-      <c r="C3" s="1"/>
-      <c r="D3" s="1"/>
-      <c r="E3" s="1"/>
-      <c r="F3" s="1"/>
-      <c r="G3" s="3" t="s">
+    <row r="1" spans="1:10" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="11"/>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
+    </row>
+    <row r="2" spans="1:10" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="11"/>
+      <c r="B2" s="11"/>
+      <c r="C2" s="11"/>
+      <c r="D2" s="11"/>
+      <c r="E2" s="11"/>
+      <c r="F2" s="11"/>
+      <c r="J2" s="5" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="11"/>
+      <c r="B3" s="11"/>
+      <c r="C3" s="11"/>
+      <c r="D3" s="11"/>
+      <c r="E3" s="11"/>
+      <c r="F3" s="11"/>
+      <c r="G3" s="12" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" ht="29" x14ac:dyDescent="0.2">
-      <c r="A4" s="1"/>
-      <c r="B4" s="1"/>
-      <c r="C4" s="1"/>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1"/>
-      <c r="F4" s="1"/>
-      <c r="G4" s="4" t="s">
+      <c r="H3" s="12"/>
+      <c r="J3" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="11"/>
+      <c r="B4" s="11"/>
+      <c r="C4" s="11"/>
+      <c r="D4" s="11"/>
+      <c r="E4" s="11"/>
+      <c r="F4" s="11"/>
+      <c r="G4" s="12"/>
+      <c r="H4" s="12"/>
+      <c r="J4" s="7" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="11"/>
+      <c r="B5" s="11"/>
+      <c r="C5" s="11"/>
+      <c r="D5" s="11"/>
+      <c r="E5" s="11"/>
+      <c r="F5" s="11"/>
+      <c r="G5" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="H4" s="2"/>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A5" s="1"/>
-      <c r="B5" s="1"/>
-      <c r="C5" s="1"/>
-      <c r="D5" s="1"/>
-      <c r="E5" s="1"/>
-      <c r="F5" s="1"/>
-      <c r="G5" s="5" t="s">
+      <c r="H5" s="13"/>
+      <c r="J5" s="8" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="11"/>
+      <c r="B6" s="11"/>
+      <c r="C6" s="11"/>
+      <c r="D6" s="11"/>
+      <c r="E6" s="11"/>
+      <c r="F6" s="11"/>
+      <c r="G6" s="13"/>
+      <c r="H6" s="13"/>
+      <c r="J6" s="9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="11"/>
+      <c r="B7" s="11"/>
+      <c r="C7" s="11"/>
+      <c r="D7" s="11"/>
+      <c r="E7" s="11"/>
+      <c r="F7" s="11"/>
+      <c r="G7" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="H5" s="2"/>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A6" s="1"/>
-      <c r="B6" s="1"/>
-      <c r="C6" s="1"/>
-      <c r="D6" s="1"/>
-      <c r="E6" s="1"/>
-      <c r="F6" s="1"/>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A7" s="1"/>
-      <c r="B7" s="1"/>
-      <c r="C7" s="1"/>
-      <c r="D7" s="1"/>
-      <c r="E7" s="1"/>
-      <c r="F7" s="1"/>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A8" s="1"/>
-      <c r="B8" s="1"/>
-      <c r="C8" s="1"/>
-      <c r="D8" s="1"/>
-      <c r="E8" s="1"/>
-      <c r="F8" s="1"/>
+      <c r="H7" s="1"/>
+      <c r="J7" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A8" s="11"/>
+      <c r="B8" s="11"/>
+      <c r="C8" s="11"/>
+      <c r="D8" s="11"/>
+      <c r="E8" s="11"/>
+      <c r="F8" s="11"/>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="3">
     <mergeCell ref="A1:F8"/>
+    <mergeCell ref="G3:H4"/>
+    <mergeCell ref="G5:H6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -619,82 +761,82 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F3419A2-BDD0-2541-8164-6EEEDA1FF00D}">
   <dimension ref="A1:H8"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.19921875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A1" s="1"/>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-    </row>
-    <row r="3" spans="1:8" ht="29" x14ac:dyDescent="0.35">
-      <c r="A3" s="1"/>
-      <c r="B3" s="1"/>
-      <c r="C3" s="1"/>
-      <c r="D3" s="1"/>
-      <c r="E3" s="1"/>
-      <c r="F3" s="1"/>
-      <c r="G3" s="3" t="s">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1" s="11"/>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2" s="11"/>
+      <c r="B2" s="11"/>
+      <c r="C2" s="11"/>
+      <c r="D2" s="11"/>
+      <c r="E2" s="11"/>
+      <c r="F2" s="11"/>
+    </row>
+    <row r="3" spans="1:8" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3" s="11"/>
+      <c r="B3" s="11"/>
+      <c r="C3" s="11"/>
+      <c r="D3" s="11"/>
+      <c r="E3" s="11"/>
+      <c r="F3" s="11"/>
+      <c r="G3" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="29" x14ac:dyDescent="0.2">
-      <c r="A4" s="1"/>
-      <c r="B4" s="1"/>
-      <c r="C4" s="1"/>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1"/>
-      <c r="F4" s="1"/>
-      <c r="G4" s="4" t="s">
+    <row r="4" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A4" s="11"/>
+      <c r="B4" s="11"/>
+      <c r="C4" s="11"/>
+      <c r="D4" s="11"/>
+      <c r="E4" s="11"/>
+      <c r="F4" s="11"/>
+      <c r="G4" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="H4" s="2"/>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A5" s="1"/>
-      <c r="B5" s="1"/>
-      <c r="C5" s="1"/>
-      <c r="D5" s="1"/>
-      <c r="E5" s="1"/>
-      <c r="F5" s="1"/>
-      <c r="G5" s="5" t="s">
+      <c r="H4" s="1"/>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A5" s="11"/>
+      <c r="B5" s="11"/>
+      <c r="C5" s="11"/>
+      <c r="D5" s="11"/>
+      <c r="E5" s="11"/>
+      <c r="F5" s="11"/>
+      <c r="G5" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="H5" s="2"/>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A6" s="1"/>
-      <c r="B6" s="1"/>
-      <c r="C6" s="1"/>
-      <c r="D6" s="1"/>
-      <c r="E6" s="1"/>
-      <c r="F6" s="1"/>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A7" s="1"/>
-      <c r="B7" s="1"/>
-      <c r="C7" s="1"/>
-      <c r="D7" s="1"/>
-      <c r="E7" s="1"/>
-      <c r="F7" s="1"/>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A8" s="1"/>
-      <c r="B8" s="1"/>
-      <c r="C8" s="1"/>
-      <c r="D8" s="1"/>
-      <c r="E8" s="1"/>
-      <c r="F8" s="1"/>
+      <c r="H5" s="1"/>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A6" s="11"/>
+      <c r="B6" s="11"/>
+      <c r="C6" s="11"/>
+      <c r="D6" s="11"/>
+      <c r="E6" s="11"/>
+      <c r="F6" s="11"/>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A7" s="11"/>
+      <c r="B7" s="11"/>
+      <c r="C7" s="11"/>
+      <c r="D7" s="11"/>
+      <c r="E7" s="11"/>
+      <c r="F7" s="11"/>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A8" s="11"/>
+      <c r="B8" s="11"/>
+      <c r="C8" s="11"/>
+      <c r="D8" s="11"/>
+      <c r="E8" s="11"/>
+      <c r="F8" s="11"/>
     </row>
   </sheetData>
   <mergeCells count="1">
